--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6207"/>
+  <dimension ref="A1:B6212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62500,6 +62500,56 @@
         <v>1.091</v>
       </c>
     </row>
+    <row r="6208">
+      <c r="A6208" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B6208" t="n">
+        <v>1.137</v>
+      </c>
+    </row>
+    <row r="6209">
+      <c r="A6209" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B6209" t="n">
+        <v>1.106</v>
+      </c>
+    </row>
+    <row r="6210">
+      <c r="A6210" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B6210" t="n">
+        <v>1.148</v>
+      </c>
+    </row>
+    <row r="6211">
+      <c r="A6211" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B6211" t="n">
+        <v>1.184</v>
+      </c>
+    </row>
+    <row r="6212">
+      <c r="A6212" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B6212" t="n">
+        <v>1.208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6212"/>
+  <dimension ref="A1:B6214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62550,6 +62550,26 @@
         <v>1.208</v>
       </c>
     </row>
+    <row r="6213">
+      <c r="A6213" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B6213" t="n">
+        <v>1.235</v>
+      </c>
+    </row>
+    <row r="6214">
+      <c r="A6214" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B6214" t="n">
+        <v>1.321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6214"/>
+  <dimension ref="A1:B6215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62570,6 +62570,16 @@
         <v>1.321</v>
       </c>
     </row>
+    <row r="6215">
+      <c r="A6215" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B6215" t="n">
+        <v>1.306</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6215"/>
+  <dimension ref="A1:B6216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62580,6 +62580,16 @@
         <v>1.306</v>
       </c>
     </row>
+    <row r="6216">
+      <c r="A6216" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B6216" t="n">
+        <v>1.229</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6216"/>
+  <dimension ref="A1:B6217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62590,6 +62590,16 @@
         <v>1.229</v>
       </c>
     </row>
+    <row r="6217">
+      <c r="A6217" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B6217" t="n">
+        <v>1.219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6217"/>
+  <dimension ref="A1:B6221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62600,6 +62600,46 @@
         <v>1.219</v>
       </c>
     </row>
+    <row r="6218">
+      <c r="A6218" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B6218" t="n">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="6219">
+      <c r="A6219" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B6219" t="n">
+        <v>1.199</v>
+      </c>
+    </row>
+    <row r="6220">
+      <c r="A6220" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B6220" t="n">
+        <v>1.213</v>
+      </c>
+    </row>
+    <row r="6221">
+      <c r="A6221" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B6221" t="n">
+        <v>1.223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6221"/>
+  <dimension ref="A1:B6224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62640,6 +62640,36 @@
         <v>1.223</v>
       </c>
     </row>
+    <row r="6222">
+      <c r="A6222" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B6222" t="n">
+        <v>1.354</v>
+      </c>
+    </row>
+    <row r="6223">
+      <c r="A6223" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B6223" t="n">
+        <v>1.416</v>
+      </c>
+    </row>
+    <row r="6224">
+      <c r="A6224" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6224" t="n">
+        <v>1.368</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6224"/>
+  <dimension ref="A1:B6226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62670,6 +62670,26 @@
         <v>1.368</v>
       </c>
     </row>
+    <row r="6225">
+      <c r="A6225" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B6225" t="n">
+        <v>1.361</v>
+      </c>
+    </row>
+    <row r="6226">
+      <c r="A6226" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B6226" t="n">
+        <v>1.327</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6226"/>
+  <dimension ref="A1:B6229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62690,6 +62690,36 @@
         <v>1.327</v>
       </c>
     </row>
+    <row r="6227">
+      <c r="A6227" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B6227" t="n">
+        <v>1.327</v>
+      </c>
+    </row>
+    <row r="6228">
+      <c r="A6228" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B6228" t="n">
+        <v>1.259</v>
+      </c>
+    </row>
+    <row r="6229">
+      <c r="A6229" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B6229" t="n">
+        <v>1.113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6229"/>
+  <dimension ref="A1:B6230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62720,6 +62720,16 @@
         <v>1.113</v>
       </c>
     </row>
+    <row r="6230">
+      <c r="A6230" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B6230" t="n">
+        <v>1.151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6230"/>
+  <dimension ref="A1:B6233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62730,6 +62730,36 @@
         <v>1.151</v>
       </c>
     </row>
+    <row r="6231">
+      <c r="A6231" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B6231" t="n">
+        <v>1.156</v>
+      </c>
+    </row>
+    <row r="6232">
+      <c r="A6232" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B6232" t="n">
+        <v>1.164</v>
+      </c>
+    </row>
+    <row r="6233">
+      <c r="A6233" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B6233" t="n">
+        <v>1.157</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6233"/>
+  <dimension ref="A1:B6235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62760,6 +62760,26 @@
         <v>1.157</v>
       </c>
     </row>
+    <row r="6234">
+      <c r="A6234" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B6234" t="n">
+        <v>1.059</v>
+      </c>
+    </row>
+    <row r="6235">
+      <c r="A6235" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B6235" t="n">
+        <v>1.128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6235"/>
+  <dimension ref="A1:B6236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62780,6 +62780,16 @@
         <v>1.128</v>
       </c>
     </row>
+    <row r="6236">
+      <c r="A6236" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B6236" t="n">
+        <v>1.158</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6236"/>
+  <dimension ref="A1:B6237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62790,6 +62790,16 @@
         <v>1.158</v>
       </c>
     </row>
+    <row r="6237">
+      <c r="A6237" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B6237" t="n">
+        <v>1.154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6237"/>
+  <dimension ref="A1:B6242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62800,6 +62800,56 @@
         <v>1.154</v>
       </c>
     </row>
+    <row r="6238">
+      <c r="A6238" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B6238" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="6239">
+      <c r="A6239" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B6239" t="n">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="6240">
+      <c r="A6240" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B6240" t="n">
+        <v>0.798</v>
+      </c>
+    </row>
+    <row r="6241">
+      <c r="A6241" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B6241" t="n">
+        <v>0.751</v>
+      </c>
+    </row>
+    <row r="6242">
+      <c r="A6242" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B6242" t="n">
+        <v>0.805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6242"/>
+  <dimension ref="A1:B6243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62850,6 +62850,16 @@
         <v>0.805</v>
       </c>
     </row>
+    <row r="6243">
+      <c r="A6243" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B6243" t="n">
+        <v>0.701</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6243"/>
+  <dimension ref="A1:B6244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62860,6 +62860,16 @@
         <v>0.701</v>
       </c>
     </row>
+    <row r="6244">
+      <c r="A6244" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B6244" t="n">
+        <v>0.617</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6244"/>
+  <dimension ref="A1:B6248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62870,6 +62870,46 @@
         <v>0.617</v>
       </c>
     </row>
+    <row r="6245">
+      <c r="A6245" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B6245" t="n">
+        <v>0.322</v>
+      </c>
+    </row>
+    <row r="6246">
+      <c r="A6246" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B6246" t="n">
+        <v>0.542</v>
+      </c>
+    </row>
+    <row r="6247">
+      <c r="A6247" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B6247" t="n">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="6248">
+      <c r="A6248" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B6248" t="n">
+        <v>0.534</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6248"/>
+  <dimension ref="A1:B6249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62910,6 +62910,16 @@
         <v>0.534</v>
       </c>
     </row>
+    <row r="6249">
+      <c r="A6249" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6249" t="n">
+        <v>0.533</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6249"/>
+  <dimension ref="A1:B6252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62920,6 +62920,36 @@
         <v>0.533</v>
       </c>
     </row>
+    <row r="6250">
+      <c r="A6250" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B6250" t="n">
+        <v>0.484</v>
+      </c>
+    </row>
+    <row r="6251">
+      <c r="A6251" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B6251" t="n">
+        <v>0.428</v>
+      </c>
+    </row>
+    <row r="6252">
+      <c r="A6252" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B6252" t="n">
+        <v>0.404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6252"/>
+  <dimension ref="A1:B6254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62950,6 +62950,26 @@
         <v>0.404</v>
       </c>
     </row>
+    <row r="6253">
+      <c r="A6253" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B6253" t="n">
+        <v>0.493</v>
+      </c>
+    </row>
+    <row r="6254">
+      <c r="A6254" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B6254" t="n">
+        <v>0.524</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6254"/>
+  <dimension ref="A1:B6257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62970,6 +62970,36 @@
         <v>0.524</v>
       </c>
     </row>
+    <row r="6255">
+      <c r="A6255" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B6255" t="n">
+        <v>0.482</v>
+      </c>
+    </row>
+    <row r="6256">
+      <c r="A6256" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B6256" t="n">
+        <v>0.496</v>
+      </c>
+    </row>
+    <row r="6257">
+      <c r="A6257" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B6257" t="n">
+        <v>0.444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6257"/>
+  <dimension ref="A1:B6258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63000,6 +63000,16 @@
         <v>0.444</v>
       </c>
     </row>
+    <row r="6258">
+      <c r="A6258" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B6258" t="n">
+        <v>0.414</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6258"/>
+  <dimension ref="A1:B6261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63010,6 +63010,36 @@
         <v>0.414</v>
       </c>
     </row>
+    <row r="6259">
+      <c r="A6259" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B6259" t="n">
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="6260">
+      <c r="A6260" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B6260" t="n">
+        <v>0.468</v>
+      </c>
+    </row>
+    <row r="6261">
+      <c r="A6261" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B6261" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6261"/>
+  <dimension ref="A1:B6263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63040,6 +63040,26 @@
         <v>0.471</v>
       </c>
     </row>
+    <row r="6262">
+      <c r="A6262" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B6262" t="n">
+        <v>0.457</v>
+      </c>
+    </row>
+    <row r="6263">
+      <c r="A6263" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B6263" t="n">
+        <v>0.355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6263"/>
+  <dimension ref="A1:B6264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63060,6 +63060,16 @@
         <v>0.355</v>
       </c>
     </row>
+    <row r="6264">
+      <c r="A6264" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B6264" t="n">
+        <v>0.338</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6264"/>
+  <dimension ref="A1:B6265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63070,6 +63070,16 @@
         <v>0.338</v>
       </c>
     </row>
+    <row r="6265">
+      <c r="A6265" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B6265" t="n">
+        <v>0.471</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6265"/>
+  <dimension ref="A1:B6267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63080,6 +63080,26 @@
         <v>0.471</v>
       </c>
     </row>
+    <row r="6266">
+      <c r="A6266" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B6266" t="n">
+        <v>0.455</v>
+      </c>
+    </row>
+    <row r="6267">
+      <c r="A6267" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B6267" t="n">
+        <v>0.402</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6267"/>
+  <dimension ref="A1:B6270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63100,6 +63100,36 @@
         <v>0.402</v>
       </c>
     </row>
+    <row r="6268">
+      <c r="A6268" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B6268" t="n">
+        <v>0.435</v>
+      </c>
+    </row>
+    <row r="6269">
+      <c r="A6269" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B6269" t="n">
+        <v>0.397</v>
+      </c>
+    </row>
+    <row r="6270">
+      <c r="A6270" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B6270" t="n">
+        <v>0.502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6270"/>
+  <dimension ref="A1:B6272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63130,6 +63130,26 @@
         <v>0.502</v>
       </c>
     </row>
+    <row r="6271">
+      <c r="A6271" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B6271" t="n">
+        <v>0.489</v>
+      </c>
+    </row>
+    <row r="6272">
+      <c r="A6272" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B6272" t="n">
+        <v>0.622</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6272"/>
+  <dimension ref="A1:B6273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63150,6 +63150,16 @@
         <v>0.622</v>
       </c>
     </row>
+    <row r="6273">
+      <c r="A6273" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B6273" t="n">
+        <v>0.574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6273"/>
+  <dimension ref="A1:B6276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63160,6 +63160,36 @@
         <v>0.574</v>
       </c>
     </row>
+    <row r="6274">
+      <c r="A6274" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B6274" t="n">
+        <v>0.483</v>
+      </c>
+    </row>
+    <row r="6275">
+      <c r="A6275" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B6275" t="n">
+        <v>0.452</v>
+      </c>
+    </row>
+    <row r="6276">
+      <c r="A6276" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B6276" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6276"/>
+  <dimension ref="A1:B6281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63190,6 +63190,56 @@
         <v>0.41</v>
       </c>
     </row>
+    <row r="6277">
+      <c r="A6277" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B6277" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="6278">
+      <c r="A6278" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B6278" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="6279">
+      <c r="A6279" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B6279" t="n">
+        <v>0.552</v>
+      </c>
+    </row>
+    <row r="6280">
+      <c r="A6280" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B6280" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+    </row>
+    <row r="6281">
+      <c r="A6281" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B6281" t="n">
+        <v>0.578</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6281"/>
+  <dimension ref="A1:B6285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63240,6 +63240,46 @@
         <v>0.578</v>
       </c>
     </row>
+    <row r="6282">
+      <c r="A6282" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B6282" t="n">
+        <v>0.586</v>
+      </c>
+    </row>
+    <row r="6283">
+      <c r="A6283" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B6283" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="6284">
+      <c r="A6284" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B6284" t="n">
+        <v>0.701</v>
+      </c>
+    </row>
+    <row r="6285">
+      <c r="A6285" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B6285" t="n">
+        <v>0.677</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6285"/>
+  <dimension ref="A1:B6287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63280,6 +63280,26 @@
         <v>0.677</v>
       </c>
     </row>
+    <row r="6286">
+      <c r="A6286" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6286" t="n">
+        <v>0.591</v>
+      </c>
+    </row>
+    <row r="6287">
+      <c r="A6287" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6287" t="n">
+        <v>0.545</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_mvrvz.xlsx
+++ b/data_cripto/btc_mvrvz.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1460"/>
+  <dimension ref="A1:B1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15030,6 +15030,16 @@
         <v>0.489</v>
       </c>
     </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>0.448</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
